--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/98.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/98.xlsx
@@ -426,13 +426,13 @@
         <v>-11.18522835049196</v>
       </c>
       <c r="E2">
-        <v>-12.07389646001644</v>
+        <v>-12.52701104074993</v>
       </c>
       <c r="F2">
-        <v>-4.25840419379958</v>
+        <v>-3.941254621596358</v>
       </c>
       <c r="G2">
-        <v>-9.567381753341426</v>
+        <v>-10.50324649292908</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-10.47578067390128</v>
       </c>
       <c r="E3">
-        <v>-13.69775289747894</v>
+        <v>-12.88463821855768</v>
       </c>
       <c r="F3">
-        <v>-3.979012436183362</v>
+        <v>-4.16779736728137</v>
       </c>
       <c r="G3">
-        <v>-9.455177433378907</v>
+        <v>-10.65760067869759</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.65630876509292</v>
       </c>
       <c r="E4">
-        <v>-12.17586863772116</v>
+        <v>-13.99061836850299</v>
       </c>
       <c r="F4">
-        <v>-3.791826254172758</v>
+        <v>-4.003900734800474</v>
       </c>
       <c r="G4">
-        <v>-9.185331555927373</v>
+        <v>-9.913006018186877</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.810260300953612</v>
       </c>
       <c r="E5">
-        <v>-12.97950974901837</v>
+        <v>-14.827788301353</v>
       </c>
       <c r="F5">
-        <v>-3.497315134720644</v>
+        <v>-3.868715316500608</v>
       </c>
       <c r="G5">
-        <v>-8.589148651942182</v>
+        <v>-8.821492669524853</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.939795995960961</v>
       </c>
       <c r="E6">
-        <v>-14.45530772880009</v>
+        <v>-15.41660766267434</v>
       </c>
       <c r="F6">
-        <v>-4.184646360254312</v>
+        <v>-4.259262382428879</v>
       </c>
       <c r="G6">
-        <v>-8.633874122177737</v>
+        <v>-9.591144849222314</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.062219710854153</v>
       </c>
       <c r="E7">
-        <v>-15.11655097492611</v>
+        <v>-16.27368023878806</v>
       </c>
       <c r="F7">
-        <v>-3.623755478349155</v>
+        <v>-4.194981071971638</v>
       </c>
       <c r="G7">
-        <v>-7.629954497939288</v>
+        <v>-9.078632673196664</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.190238748047451</v>
       </c>
       <c r="E8">
-        <v>-15.77379105002934</v>
+        <v>-16.99684583849496</v>
       </c>
       <c r="F8">
-        <v>-3.540436628240775</v>
+        <v>-4.078945022922289</v>
       </c>
       <c r="G8">
-        <v>-7.275510939777218</v>
+        <v>-8.884022253670606</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.342012055847664</v>
       </c>
       <c r="E9">
-        <v>-17.14495863786384</v>
+        <v>-17.47121707622046</v>
       </c>
       <c r="F9">
-        <v>-3.863200874700172</v>
+        <v>-3.982688730716986</v>
       </c>
       <c r="G9">
-        <v>-7.339192593770639</v>
+        <v>-7.865493191967355</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.519679987720465</v>
       </c>
       <c r="E10">
-        <v>-17.60469837607054</v>
+        <v>-18.42203359276695</v>
       </c>
       <c r="F10">
-        <v>-3.885729154586707</v>
+        <v>-4.469299079245708</v>
       </c>
       <c r="G10">
-        <v>-6.881526225694094</v>
+        <v>-7.341294790188076</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-3.747347231415358</v>
       </c>
       <c r="E11">
-        <v>-17.50794752889667</v>
+        <v>-19.32218554211564</v>
       </c>
       <c r="F11">
-        <v>-3.809975783968095</v>
+        <v>-4.478538689256534</v>
       </c>
       <c r="G11">
-        <v>-6.245851823970937</v>
+        <v>-6.818059757160726</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-3.038770373120836</v>
       </c>
       <c r="E12">
-        <v>-18.89590216987759</v>
+        <v>-19.49143272967831</v>
       </c>
       <c r="F12">
-        <v>-3.925803084431939</v>
+        <v>-4.170847416058478</v>
       </c>
       <c r="G12">
-        <v>-6.091242726195894</v>
+        <v>-6.514403278116616</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-2.403309131096272</v>
       </c>
       <c r="E13">
-        <v>-18.69785388762614</v>
+        <v>-19.42254105459962</v>
       </c>
       <c r="F13">
-        <v>-3.521978117404194</v>
+        <v>-4.000322187620379</v>
       </c>
       <c r="G13">
-        <v>-6.293411121188107</v>
+        <v>-6.307752404464229</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-1.865595040554472</v>
       </c>
       <c r="E14">
-        <v>-20.70320256091681</v>
+        <v>-21.00410154483048</v>
       </c>
       <c r="F14">
-        <v>-3.997149540467658</v>
+        <v>-3.998095536041654</v>
       </c>
       <c r="G14">
-        <v>-5.925268525584533</v>
+        <v>-5.734061346872847</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-1.431976538489585</v>
       </c>
       <c r="E15">
-        <v>-21.70339755804295</v>
+        <v>-22.72072830081411</v>
       </c>
       <c r="F15">
-        <v>-3.461142815342598</v>
+        <v>-4.102586628598186</v>
       </c>
       <c r="G15">
-        <v>-4.362912837599664</v>
+        <v>-4.918909029283641</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-1.104974424343768</v>
       </c>
       <c r="E16">
-        <v>-21.93264249773324</v>
+        <v>-22.9955478029176</v>
       </c>
       <c r="F16">
-        <v>-3.258071031648508</v>
+        <v>-3.699268622420955</v>
       </c>
       <c r="G16">
-        <v>-4.254204453726616</v>
+        <v>-5.191648323536499</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-0.8881095043603361</v>
       </c>
       <c r="E17">
-        <v>-22.80706818624435</v>
+        <v>-23.68028930066942</v>
       </c>
       <c r="F17">
-        <v>-3.579576988023052</v>
+        <v>-3.565443383396487</v>
       </c>
       <c r="G17">
-        <v>-3.988900644754962</v>
+        <v>-4.856058322220578</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.7676079801897717</v>
       </c>
       <c r="E18">
-        <v>-23.41494336618997</v>
+        <v>-24.75606000050957</v>
       </c>
       <c r="F18">
-        <v>-2.476370534853115</v>
+        <v>-3.158373701251976</v>
       </c>
       <c r="G18">
-        <v>-3.459743045757856</v>
+        <v>-4.726764966184342</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.728459203765538</v>
       </c>
       <c r="E19">
-        <v>-23.76472722701644</v>
+        <v>-26.01056504095845</v>
       </c>
       <c r="F19">
-        <v>-2.766068839694964</v>
+        <v>-2.99719328548486</v>
       </c>
       <c r="G19">
-        <v>-3.285191221654243</v>
+        <v>-4.047487369163444</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.752412365702524</v>
       </c>
       <c r="E20">
-        <v>-24.62733359836753</v>
+        <v>-25.69677802001896</v>
       </c>
       <c r="F20">
-        <v>-2.028345539946794</v>
+        <v>-2.535197874330325</v>
       </c>
       <c r="G20">
-        <v>-4.021165221580699</v>
+        <v>-4.466129026423061</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.8131349314455124</v>
       </c>
       <c r="E21">
-        <v>-25.86528253784438</v>
+        <v>-26.69731718116968</v>
       </c>
       <c r="F21">
-        <v>-2.247301268589565</v>
+        <v>-2.288854662616196</v>
       </c>
       <c r="G21">
-        <v>-3.640836507847068</v>
+        <v>-4.202599669860456</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.8912002978740738</v>
       </c>
       <c r="E22">
-        <v>-25.49773347348582</v>
+        <v>-27.36586032739606</v>
       </c>
       <c r="F22">
-        <v>-2.196350874745576</v>
+        <v>-2.278384927012214</v>
       </c>
       <c r="G22">
-        <v>-2.898380459754719</v>
+        <v>-4.52936375676868</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.9689110432870237</v>
       </c>
       <c r="E23">
-        <v>-27.50694493510503</v>
+        <v>-27.66561360738579</v>
       </c>
       <c r="F23">
-        <v>-1.124088914274617</v>
+        <v>-1.987098641859198</v>
       </c>
       <c r="G23">
-        <v>-4.13730578018941</v>
+        <v>-4.527675378543651</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.031238585151067</v>
       </c>
       <c r="E24">
-        <v>-27.64058473154539</v>
+        <v>-28.25316499598499</v>
       </c>
       <c r="F24">
-        <v>-1.690802390654051</v>
+        <v>-1.761633602165229</v>
       </c>
       <c r="G24">
-        <v>-3.267181853920608</v>
+        <v>-3.735729985184737</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.07287621152777</v>
       </c>
       <c r="E25">
-        <v>-26.92566095453245</v>
+        <v>-28.39956150370495</v>
       </c>
       <c r="F25">
-        <v>-1.069716534689663</v>
+        <v>-1.832200564474913</v>
       </c>
       <c r="G25">
-        <v>-3.519551361470329</v>
+        <v>-4.018715417881638</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.091141185840909</v>
       </c>
       <c r="E26">
-        <v>-27.03649082739618</v>
+        <v>-28.41442395539813</v>
       </c>
       <c r="F26">
-        <v>-1.328515907039688</v>
+        <v>-1.561563821938884</v>
       </c>
       <c r="G26">
-        <v>-3.755672711513307</v>
+        <v>-4.373069591314148</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.086028774380803</v>
       </c>
       <c r="E27">
-        <v>-27.83173614788317</v>
+        <v>-28.75135147851682</v>
       </c>
       <c r="F27">
-        <v>-1.308647514883541</v>
+        <v>-1.591687402541688</v>
       </c>
       <c r="G27">
-        <v>-2.571811695033313</v>
+        <v>-4.742840975323043</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.061528457267604</v>
       </c>
       <c r="E28">
-        <v>-27.95067198922062</v>
+        <v>-28.29456430536311</v>
       </c>
       <c r="F28">
-        <v>-1.366763286761747</v>
+        <v>-0.985259507769837</v>
       </c>
       <c r="G28">
-        <v>-4.444868702969861</v>
+        <v>-4.678884546049863</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-1.020806412598199</v>
       </c>
       <c r="E29">
-        <v>-27.24274923302354</v>
+        <v>-28.74387949640416</v>
       </c>
       <c r="F29">
-        <v>-1.081647510392185</v>
+        <v>-1.311077944843355</v>
       </c>
       <c r="G29">
-        <v>-3.954951000249736</v>
+        <v>-4.777201127475139</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.9668673855059368</v>
       </c>
       <c r="E30">
-        <v>-26.53572764315398</v>
+        <v>-27.91570311293339</v>
       </c>
       <c r="F30">
-        <v>-1.250303941969567</v>
+        <v>-1.395400776243928</v>
       </c>
       <c r="G30">
-        <v>-3.44173698856976</v>
+        <v>-4.065652332537425</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.902476471005432</v>
       </c>
       <c r="E31">
-        <v>-26.83560319194191</v>
+        <v>-28.47094836796187</v>
       </c>
       <c r="F31">
-        <v>-1.686276191165155</v>
+        <v>-1.518979110495767</v>
       </c>
       <c r="G31">
-        <v>-3.510083201228013</v>
+        <v>-4.646811980865404</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.8285686025798581</v>
       </c>
       <c r="E32">
-        <v>-26.38909112631161</v>
+        <v>-28.14287854000218</v>
       </c>
       <c r="F32">
-        <v>-1.376575298647907</v>
+        <v>-1.362592456888651</v>
       </c>
       <c r="G32">
-        <v>-3.128916919472946</v>
+        <v>-4.49593055736758</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.7450232502158771</v>
       </c>
       <c r="E33">
-        <v>-27.3241394963634</v>
+        <v>-27.64677968398789</v>
       </c>
       <c r="F33">
-        <v>-1.250387607077249</v>
+        <v>-1.205431279759918</v>
       </c>
       <c r="G33">
-        <v>-3.694742120863021</v>
+        <v>-4.72513948832456</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.6510458456222589</v>
       </c>
       <c r="E34">
-        <v>-24.88603626147772</v>
+        <v>-27.04613647703251</v>
       </c>
       <c r="F34">
-        <v>-1.256698109951776</v>
+        <v>-1.761978203004793</v>
       </c>
       <c r="G34">
-        <v>-4.147661166636251</v>
+        <v>-4.632503803044673</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.5454632890240041</v>
       </c>
       <c r="E35">
-        <v>-24.18972904111031</v>
+        <v>-26.58678618759046</v>
       </c>
       <c r="F35">
-        <v>-1.286516022982947</v>
+        <v>-1.561859549101683</v>
       </c>
       <c r="G35">
-        <v>-3.165677217141014</v>
+        <v>-5.085998883741737</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.427581546754037</v>
       </c>
       <c r="E36">
-        <v>-24.48836831649415</v>
+        <v>-26.46649180405071</v>
       </c>
       <c r="F36">
-        <v>-1.272544778367331</v>
+        <v>-1.682029979858405</v>
       </c>
       <c r="G36">
-        <v>-4.479867790411036</v>
+        <v>-5.062249030043006</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.2975635825574234</v>
       </c>
       <c r="E37">
-        <v>-26.11206625736638</v>
+        <v>-26.44556119718725</v>
       </c>
       <c r="F37">
-        <v>-1.618979623361723</v>
+        <v>-1.767042841305509</v>
       </c>
       <c r="G37">
-        <v>-3.845921493459379</v>
+        <v>-5.040240523297931</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.1567405535217777</v>
       </c>
       <c r="E38">
-        <v>-24.4875124349067</v>
+        <v>-24.94307692007834</v>
       </c>
       <c r="F38">
-        <v>-1.595876456497645</v>
+        <v>-1.821449183953978</v>
       </c>
       <c r="G38">
-        <v>-3.764366204099433</v>
+        <v>-4.783640138549021</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.006943314391583266</v>
       </c>
       <c r="E39">
-        <v>-23.5979163584699</v>
+        <v>-24.66030088914337</v>
       </c>
       <c r="F39">
-        <v>-1.386638305857115</v>
+        <v>-1.87687441850789</v>
       </c>
       <c r="G39">
-        <v>-3.929284340683767</v>
+        <v>-5.285505600120376</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.1492753634620526</v>
       </c>
       <c r="E40">
-        <v>-22.58665377086901</v>
+        <v>-24.82550414941719</v>
       </c>
       <c r="F40">
-        <v>-1.67782104508478</v>
+        <v>-1.972484584139009</v>
       </c>
       <c r="G40">
-        <v>-2.931810348610279</v>
+        <v>-4.605301050348483</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.3088669690359647</v>
       </c>
       <c r="E41">
-        <v>-22.65615226146473</v>
+        <v>-24.13063245531021</v>
       </c>
       <c r="F41">
-        <v>-1.397681271703835</v>
+        <v>-1.848218704942847</v>
       </c>
       <c r="G41">
-        <v>-4.174026351311007</v>
+        <v>-4.74757836598974</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>0.4684231338214133</v>
       </c>
       <c r="E42">
-        <v>-21.95555657621206</v>
+        <v>-22.32166105736217</v>
       </c>
       <c r="F42">
-        <v>-1.92743133783555</v>
+        <v>-2.260521183970842</v>
       </c>
       <c r="G42">
-        <v>-4.181935244604325</v>
+        <v>-4.875540882719189</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.6237874531379815</v>
       </c>
       <c r="E43">
-        <v>-21.24248041659424</v>
+        <v>-22.2337724338213</v>
       </c>
       <c r="F43">
-        <v>-1.549948454216829</v>
+        <v>-2.285336586256507</v>
       </c>
       <c r="G43">
-        <v>-4.224459202056265</v>
+        <v>-4.553077194466479</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>0.7696315631510887</v>
       </c>
       <c r="E44">
-        <v>-20.49609280217601</v>
+        <v>-21.30029544425017</v>
       </c>
       <c r="F44">
-        <v>-1.729075449765597</v>
+        <v>-2.069682730081295</v>
       </c>
       <c r="G44">
-        <v>-5.216752190360792</v>
+        <v>-4.654177944690282</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>0.8993421576812486</v>
       </c>
       <c r="E45">
-        <v>-20.26731882378251</v>
+        <v>-20.7736248602101</v>
       </c>
       <c r="F45">
-        <v>-1.786767097533569</v>
+        <v>-2.146816989160374</v>
       </c>
       <c r="G45">
-        <v>-4.43796952606602</v>
+        <v>-4.996398968721363</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>1.00560076746593</v>
       </c>
       <c r="E46">
-        <v>-20.96905568448512</v>
+        <v>-20.05384655906093</v>
       </c>
       <c r="F46">
-        <v>-1.747729455309239</v>
+        <v>-2.22137916745376</v>
       </c>
       <c r="G46">
-        <v>-5.517406004600783</v>
+        <v>-4.246901390266983</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>1.081490674364217</v>
       </c>
       <c r="E47">
-        <v>-19.46577892442486</v>
+        <v>-19.80252983705725</v>
       </c>
       <c r="F47">
-        <v>-1.291850709056976</v>
+        <v>-2.260335629672615</v>
       </c>
       <c r="G47">
-        <v>-4.57328807498373</v>
+        <v>-4.733793254364214</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>1.121081484985526</v>
       </c>
       <c r="E48">
-        <v>-17.59106766930746</v>
+        <v>-18.67241744912506</v>
       </c>
       <c r="F48">
-        <v>-1.852179129495632</v>
+        <v>-2.331306006907463</v>
       </c>
       <c r="G48">
-        <v>-3.874683513104567</v>
+        <v>-4.181259893314315</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>1.121122971828947</v>
       </c>
       <c r="E49">
-        <v>-16.98008142771857</v>
+        <v>-18.75312844136376</v>
       </c>
       <c r="F49">
-        <v>-1.785850923186072</v>
+        <v>-1.914083853874241</v>
       </c>
       <c r="G49">
-        <v>-4.818496872532007</v>
+        <v>-4.92255393992238</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>1.079599395362127</v>
       </c>
       <c r="E50">
-        <v>-17.39237181527291</v>
+        <v>-18.51402501375877</v>
       </c>
       <c r="F50">
-        <v>-1.860156307584591</v>
+        <v>-2.308615367009979</v>
       </c>
       <c r="G50">
-        <v>-3.972033415232375</v>
+        <v>-4.647229109603352</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>0.9964014217359837</v>
       </c>
       <c r="E51">
-        <v>-16.53206590871772</v>
+        <v>-17.38105515872774</v>
       </c>
       <c r="F51">
-        <v>-1.902867759240336</v>
+        <v>-2.363732448890049</v>
       </c>
       <c r="G51">
-        <v>-4.164766755437666</v>
+        <v>-5.209227320350029</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>0.8739635150692285</v>
       </c>
       <c r="E52">
-        <v>-16.5745067671176</v>
+        <v>-17.03483973541931</v>
       </c>
       <c r="F52">
-        <v>-1.641641270400109</v>
+        <v>-2.346916590613219</v>
       </c>
       <c r="G52">
-        <v>-5.74749223012567</v>
+        <v>-5.568736013187183</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>0.7136375454806158</v>
       </c>
       <c r="E53">
-        <v>-15.79228080940266</v>
+        <v>-16.74638046960472</v>
       </c>
       <c r="F53">
-        <v>-1.531331725206313</v>
+        <v>-2.417433850878736</v>
       </c>
       <c r="G53">
-        <v>-4.709566682107829</v>
+        <v>-5.954778728521596</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>0.5181520416777808</v>
       </c>
       <c r="E54">
-        <v>-14.12630956366883</v>
+        <v>-16.47181909051967</v>
       </c>
       <c r="F54">
-        <v>-2.357884175026285</v>
+        <v>-2.607202054083866</v>
       </c>
       <c r="G54">
-        <v>-4.398640245059478</v>
+        <v>-5.362237424629604</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>0.2915143630366688</v>
       </c>
       <c r="E55">
-        <v>-12.89375403673512</v>
+        <v>-15.8683455873095</v>
       </c>
       <c r="F55">
-        <v>-1.331405252540652</v>
+        <v>-2.381496787843085</v>
       </c>
       <c r="G55">
-        <v>-5.250066210122478</v>
+        <v>-5.826415635781895</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>0.03628127898500475</v>
       </c>
       <c r="E56">
-        <v>-14.24654960552049</v>
+        <v>-15.53559331722588</v>
       </c>
       <c r="F56">
-        <v>-1.571389087703489</v>
+        <v>-2.457936875038618</v>
       </c>
       <c r="G56">
-        <v>-5.384229378646982</v>
+        <v>-5.97161285258879</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-0.2432089072243299</v>
       </c>
       <c r="E57">
-        <v>-13.13523491319414</v>
+        <v>-14.41509035113797</v>
       </c>
       <c r="F57">
-        <v>-2.333404261538754</v>
+        <v>-2.510993807187926</v>
       </c>
       <c r="G57">
-        <v>-5.327764713929173</v>
+        <v>-6.272925465391096</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-0.541633339599157</v>
       </c>
       <c r="E58">
-        <v>-13.31795431092963</v>
+        <v>-13.08289481061349</v>
       </c>
       <c r="F58">
-        <v>-1.655067449264684</v>
+        <v>-2.410596506336029</v>
       </c>
       <c r="G58">
-        <v>-6.798987704308985</v>
+        <v>-6.167928203067572</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-0.8538689399024351</v>
       </c>
       <c r="E59">
-        <v>-12.21063826115205</v>
+        <v>-14.5673104764318</v>
       </c>
       <c r="F59">
-        <v>-2.256147404084061</v>
+        <v>-2.484506759483412</v>
       </c>
       <c r="G59">
-        <v>-5.709612968065329</v>
+        <v>-6.383798946046828</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-1.172285582303982</v>
       </c>
       <c r="E60">
-        <v>-11.62457674050138</v>
+        <v>-13.26869357067419</v>
       </c>
       <c r="F60">
-        <v>-1.504306238689979</v>
+        <v>-2.759430303328929</v>
       </c>
       <c r="G60">
-        <v>-5.631838321711231</v>
+        <v>-6.922732586021402</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-1.490130959566186</v>
       </c>
       <c r="E61">
-        <v>-13.17778445497021</v>
+        <v>-12.78507971749905</v>
       </c>
       <c r="F61">
-        <v>-1.648196970025865</v>
+        <v>-2.54711808125661</v>
       </c>
       <c r="G61">
-        <v>-5.841087973611945</v>
+        <v>-6.636880220887492</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-1.802089548924493</v>
       </c>
       <c r="E62">
-        <v>-9.655428688428024</v>
+        <v>-13.29735428266874</v>
       </c>
       <c r="F62">
-        <v>-1.868600684888729</v>
+        <v>-2.457200456417529</v>
       </c>
       <c r="G62">
-        <v>-6.670955666123211</v>
+        <v>-6.455263692603075</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-2.100131902370971</v>
       </c>
       <c r="E63">
-        <v>-11.86545532991738</v>
+        <v>-12.55602497371707</v>
       </c>
       <c r="F63">
-        <v>-2.466683606444778</v>
+        <v>-2.446814385921229</v>
       </c>
       <c r="G63">
-        <v>-7.6824067814635</v>
+        <v>-6.811514808629586</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.379814960865766</v>
       </c>
       <c r="E64">
-        <v>-10.75454367177771</v>
+        <v>-11.98908719880079</v>
       </c>
       <c r="F64">
-        <v>-2.053749911455849</v>
+        <v>-2.182509683812199</v>
       </c>
       <c r="G64">
-        <v>-6.57279799088382</v>
+        <v>-7.654538609113916</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.636955502447344</v>
       </c>
       <c r="E65">
-        <v>-10.07879572340513</v>
+        <v>-12.00518139542405</v>
       </c>
       <c r="F65">
-        <v>-1.887483319835544</v>
+        <v>-2.566829911973627</v>
       </c>
       <c r="G65">
-        <v>-7.477381385670897</v>
+        <v>-8.03689668726312</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.864815503042783</v>
       </c>
       <c r="E66">
-        <v>-10.42113024448897</v>
+        <v>-11.84924792144393</v>
       </c>
       <c r="F66">
-        <v>-1.907888494068704</v>
+        <v>-2.81022165063158</v>
       </c>
       <c r="G66">
-        <v>-7.282287626496107</v>
+        <v>-7.618337793641985</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.062010264309678</v>
       </c>
       <c r="E67">
-        <v>-10.07991425648502</v>
+        <v>-11.62687720529727</v>
       </c>
       <c r="F67">
-        <v>-2.235158230831927</v>
+        <v>-2.627925321399701</v>
       </c>
       <c r="G67">
-        <v>-7.051188374036203</v>
+        <v>-7.841703611722152</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.226066184728384</v>
       </c>
       <c r="E68">
-        <v>-10.7285592879217</v>
+        <v>-11.90793694458334</v>
       </c>
       <c r="F68">
-        <v>-2.253982051693143</v>
+        <v>-2.571810056799257</v>
       </c>
       <c r="G68">
-        <v>-7.153159797736834</v>
+        <v>-7.263665807837707</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.352924357129472</v>
       </c>
       <c r="E69">
-        <v>-9.815976677421961</v>
+        <v>-11.32163541481025</v>
       </c>
       <c r="F69">
-        <v>-2.259115444488291</v>
+        <v>-2.489639323911157</v>
       </c>
       <c r="G69">
-        <v>-8.059570613661588</v>
+        <v>-7.498472871301594</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.443449831081008</v>
       </c>
       <c r="E70">
-        <v>-11.15515512486627</v>
+        <v>-10.48278994657741</v>
       </c>
       <c r="F70">
-        <v>-2.265457425324124</v>
+        <v>-2.797353791396493</v>
       </c>
       <c r="G70">
-        <v>-7.736037619199694</v>
+        <v>-7.015215986206482</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.49583459585851</v>
       </c>
       <c r="E71">
-        <v>-11.37980819191279</v>
+        <v>-11.52686585683788</v>
       </c>
       <c r="F71">
-        <v>-2.152297467897295</v>
+        <v>-2.708044188231067</v>
       </c>
       <c r="G71">
-        <v>-7.456554743683342</v>
+        <v>-7.618642363831598</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.508867126287598</v>
       </c>
       <c r="E72">
-        <v>-10.9159475423591</v>
+        <v>-10.90113490388001</v>
       </c>
       <c r="F72">
-        <v>-2.735410962117354</v>
+        <v>-2.59035471784573</v>
       </c>
       <c r="G72">
-        <v>-7.021290837271045</v>
+        <v>-8.22890170744977</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.486479591883508</v>
       </c>
       <c r="E73">
-        <v>-10.343217849187</v>
+        <v>-12.01835925478637</v>
       </c>
       <c r="F73">
-        <v>-2.826307717226544</v>
+        <v>-3.065839263787451</v>
       </c>
       <c r="G73">
-        <v>-6.776744148830621</v>
+        <v>-7.705842133336001</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.429256118256</v>
       </c>
       <c r="E74">
-        <v>-10.02692658212127</v>
+        <v>-11.08948319480703</v>
       </c>
       <c r="F74">
-        <v>-2.654009782546455</v>
+        <v>-2.978587325250579</v>
       </c>
       <c r="G74">
-        <v>-6.504325977495074</v>
+        <v>-7.296483245768502</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.339908956108201</v>
       </c>
       <c r="E75">
-        <v>-10.9431636711452</v>
+        <v>-11.76610966713711</v>
       </c>
       <c r="F75">
-        <v>-2.677255428603815</v>
+        <v>-2.688757309991686</v>
       </c>
       <c r="G75">
-        <v>-6.18710288283103</v>
+        <v>-7.706007660612965</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.224451117676554</v>
       </c>
       <c r="E76">
-        <v>-10.01741678670516</v>
+        <v>-12.56510456410245</v>
       </c>
       <c r="F76">
-        <v>-2.213102120364987</v>
+        <v>-2.382592717916989</v>
       </c>
       <c r="G76">
-        <v>-5.874567520650595</v>
+        <v>-7.532816470725993</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.085070696256482</v>
       </c>
       <c r="E77">
-        <v>-11.82451339641403</v>
+        <v>-12.85155318745764</v>
       </c>
       <c r="F77">
-        <v>-2.281275100880581</v>
+        <v>-2.825607746771178</v>
       </c>
       <c r="G77">
-        <v>-6.506861855378156</v>
+        <v>-6.913079035228887</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.928030816519611</v>
       </c>
       <c r="E78">
-        <v>-12.45145798040596</v>
+        <v>-13.70701362682462</v>
       </c>
       <c r="F78">
-        <v>-3.165593751534777</v>
+        <v>-2.919980331502515</v>
       </c>
       <c r="G78">
-        <v>-6.641879144651792</v>
+        <v>-6.750544491432829</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.759559518105451</v>
       </c>
       <c r="E79">
-        <v>-12.13884836270845</v>
+        <v>-14.19986103850141</v>
       </c>
       <c r="F79">
-        <v>-2.40086484608794</v>
+        <v>-3.071840785620734</v>
       </c>
       <c r="G79">
-        <v>-5.77438379154117</v>
+        <v>-7.204711612874365</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.580808809890202</v>
       </c>
       <c r="E80">
-        <v>-13.53210131827836</v>
+        <v>-14.431048693541</v>
       </c>
       <c r="F80">
-        <v>-3.040242711040947</v>
+        <v>-2.747735412336205</v>
       </c>
       <c r="G80">
-        <v>-5.311109359321099</v>
+        <v>-6.658498083258933</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.399329125325695</v>
       </c>
       <c r="E81">
-        <v>-13.80101569027584</v>
+        <v>-14.59952604052237</v>
       </c>
       <c r="F81">
-        <v>-3.036833150811024</v>
+        <v>-3.106266906513679</v>
       </c>
       <c r="G81">
-        <v>-5.057994979025042</v>
+        <v>-6.354543655116289</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.220769343274714</v>
       </c>
       <c r="E82">
-        <v>-14.44225213823598</v>
+        <v>-15.00837931630488</v>
       </c>
       <c r="F82">
-        <v>-2.790940570964019</v>
+        <v>-2.936744831000371</v>
       </c>
       <c r="G82">
-        <v>-4.837962880302922</v>
+        <v>-6.839651135167853</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.047454638479234</v>
       </c>
       <c r="E83">
-        <v>-16.39084997526252</v>
+        <v>-16.49473316899848</v>
       </c>
       <c r="F83">
-        <v>-2.763221740931542</v>
+        <v>-3.158292521246502</v>
       </c>
       <c r="G83">
-        <v>-4.459994585538792</v>
+        <v>-6.13572983715262</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.889899787725928</v>
       </c>
       <c r="E84">
-        <v>-15.55885608820329</v>
+        <v>-17.73948387643485</v>
       </c>
       <c r="F84">
-        <v>-2.774117257380564</v>
+        <v>-3.171136357826908</v>
       </c>
       <c r="G84">
-        <v>-3.926549830068328</v>
+        <v>-5.423366648012246</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.755081103860229</v>
       </c>
       <c r="E85">
-        <v>-17.51727165687846</v>
+        <v>-18.29749602908201</v>
       </c>
       <c r="F85">
-        <v>-3.051123316876718</v>
+        <v>-3.112230323446432</v>
       </c>
       <c r="G85">
-        <v>-5.190727991876581</v>
+        <v>-5.149710332645011</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.648548386662681</v>
       </c>
       <c r="E86">
-        <v>-18.60595303611448</v>
+        <v>-19.29142361818153</v>
       </c>
       <c r="F86">
-        <v>-2.466986788914202</v>
+        <v>-3.200554169402527</v>
       </c>
       <c r="G86">
-        <v>-5.90338913011549</v>
+        <v>-5.287131077980158</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.582744775245948</v>
       </c>
       <c r="E87">
-        <v>-20.27041177152975</v>
+        <v>-20.82296258452366</v>
       </c>
       <c r="F87">
-        <v>-2.969368424424824</v>
+        <v>-3.301635701729137</v>
       </c>
       <c r="G87">
-        <v>-4.063659384122784</v>
+        <v>-5.370460819749153</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.562156219053486</v>
       </c>
       <c r="E88">
-        <v>-20.55135829896562</v>
+        <v>-21.49900488370675</v>
       </c>
       <c r="F88">
-        <v>-2.826415404988908</v>
+        <v>-2.865822499074886</v>
       </c>
       <c r="G88">
-        <v>-4.738689551216797</v>
+        <v>-5.224200917824152</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.592067248130483</v>
       </c>
       <c r="E89">
-        <v>-23.05164653892462</v>
+        <v>-23.83412609118399</v>
       </c>
       <c r="F89">
-        <v>-3.540666086011351</v>
+        <v>-3.418189480405236</v>
       </c>
       <c r="G89">
-        <v>-3.770139795519922</v>
+        <v>-4.956980302985261</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.681284712262608</v>
       </c>
       <c r="E90">
-        <v>-23.44816877998425</v>
+        <v>-24.13355784951917</v>
       </c>
       <c r="F90">
-        <v>-2.733843690991257</v>
+        <v>-3.246661099042347</v>
       </c>
       <c r="G90">
-        <v>-5.049387560622937</v>
+        <v>-5.378121422127027</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.828684133114541</v>
       </c>
       <c r="E91">
-        <v>-25.90007933211932</v>
+        <v>-26.62090371076425</v>
       </c>
       <c r="F91">
-        <v>-3.776823692140656</v>
+        <v>-3.217423043193136</v>
       </c>
       <c r="G91">
-        <v>-4.189953385900441</v>
+        <v>-5.013931617897343</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.036236295539463</v>
       </c>
       <c r="E92">
-        <v>-26.98777350402166</v>
+        <v>-28.07563070098828</v>
       </c>
       <c r="F92">
-        <v>-2.83779054616415</v>
+        <v>-3.200977465145357</v>
       </c>
       <c r="G92">
-        <v>-4.696877361055802</v>
+        <v>-5.785586677646064</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.303989143117252</v>
       </c>
       <c r="E93">
-        <v>-28.43592967846055</v>
+        <v>-29.3677673604409</v>
       </c>
       <c r="F93">
-        <v>-2.911469684806153</v>
+        <v>-3.183527905805386</v>
       </c>
       <c r="G93">
-        <v>-5.117561624913149</v>
+        <v>-5.526261713918334</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.620470193251847</v>
       </c>
       <c r="E94">
-        <v>-31.34505987301706</v>
+        <v>-31.85556833332376</v>
       </c>
       <c r="F94">
-        <v>-3.352788217219409</v>
+        <v>-3.09536641986024</v>
       </c>
       <c r="G94">
-        <v>-4.724709117404455</v>
+        <v>-5.834225212709036</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.979701962866931</v>
       </c>
       <c r="E95">
-        <v>-31.20343411266417</v>
+        <v>-32.94004502444365</v>
       </c>
       <c r="F95">
-        <v>-3.089229874140301</v>
+        <v>-3.282970927409258</v>
       </c>
       <c r="G95">
-        <v>-4.498857079624296</v>
+        <v>-6.180468549570331</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.369089583989748</v>
       </c>
       <c r="E96">
-        <v>-34.46365236856135</v>
+        <v>-35.59359946719226</v>
       </c>
       <c r="F96">
-        <v>-3.668477377691495</v>
+        <v>-3.35418815813014</v>
       </c>
       <c r="G96">
-        <v>-5.069565335684795</v>
+        <v>-5.818890765771132</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.764302280712933</v>
       </c>
       <c r="E97">
-        <v>-36.66953772057069</v>
+        <v>-38.40024350224417</v>
       </c>
       <c r="F97">
-        <v>-3.599898497148529</v>
+        <v>-3.503106251233616</v>
       </c>
       <c r="G97">
-        <v>-6.094814804832767</v>
+        <v>-6.333296573845246</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.155671362696074</v>
       </c>
       <c r="E98">
-        <v>-39.36399334055658</v>
+        <v>-39.99502260810342</v>
       </c>
       <c r="F98">
-        <v>-3.606820335166322</v>
+        <v>-3.214648012393758</v>
       </c>
       <c r="G98">
-        <v>-5.472074704531543</v>
+        <v>-6.529092168674362</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.518003381084982</v>
       </c>
       <c r="E99">
-        <v>-41.58531852469507</v>
+        <v>-41.9878636361849</v>
       </c>
       <c r="F99">
-        <v>-4.077070427489754</v>
+        <v>-3.459043732343904</v>
       </c>
       <c r="G99">
-        <v>-5.177601678813371</v>
+        <v>-6.284704386419824</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.843103861167482</v>
       </c>
       <c r="E100">
-        <v>-44.26391316446909</v>
+        <v>-44.8434989672888</v>
       </c>
       <c r="F100">
-        <v>-3.690698333271591</v>
+        <v>-3.637351472531303</v>
       </c>
       <c r="G100">
-        <v>-5.494308328373288</v>
+        <v>-7.102673978262948</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.106537522457732</v>
       </c>
       <c r="E101">
-        <v>-45.95187241574717</v>
+        <v>-46.98139607478398</v>
       </c>
       <c r="F101">
-        <v>-4.285730377683129</v>
+        <v>-3.937908845656451</v>
       </c>
       <c r="G101">
-        <v>-6.215043887182479</v>
+        <v>-6.670627922114822</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.326247888343818</v>
       </c>
       <c r="E102">
-        <v>-48.57587403712171</v>
+        <v>-48.74383966654022</v>
       </c>
       <c r="F102">
-        <v>-4.315894548288671</v>
+        <v>-3.612064729193446</v>
       </c>
       <c r="G102">
-        <v>-6.556741845018355</v>
+        <v>-7.158605645148935</v>
       </c>
     </row>
   </sheetData>
